--- a/data/trans_dic/P36B02_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36B02_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>89,77; 93,22</t>
+          <t>89,77; 93,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,44; 93,19</t>
+          <t>89,45; 93,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,87; 93,03</t>
+          <t>88,89; 92,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81,94; 87,75</t>
+          <t>81,6; 87,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,74; 95,24</t>
+          <t>92,77; 95,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,56; 95,98</t>
+          <t>93,59; 96,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,15; 96,84</t>
+          <t>94,39; 97,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,8; 91,26</t>
+          <t>87,91; 91,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,97</t>
+          <t>91,88; 94,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92,28; 94,45</t>
+          <t>92,37; 94,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92,53; 94,79</t>
+          <t>92,47; 94,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,06; 89,26</t>
+          <t>85,76; 89,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,64; 94,19</t>
+          <t>91,52; 94,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,87; 95,07</t>
+          <t>92,86; 95,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,81; 92,31</t>
+          <t>89,82; 92,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,73; 92,27</t>
+          <t>85,64; 88,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,36; 94,81</t>
+          <t>92,47; 94,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,35; 94,77</t>
+          <t>92,29; 94,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,56; 94,76</t>
+          <t>92,62; 94,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,71; 91,0</t>
+          <t>87,4; 89,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,42; 94,23</t>
+          <t>92,41; 94,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92,97; 94,65</t>
+          <t>92,95; 94,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91,51; 93,26</t>
+          <t>91,6; 93,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,43; 90,3</t>
+          <t>86,91; 89,06</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,98%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,42; 96,55</t>
+          <t>92,73; 96,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,31; 96,36</t>
+          <t>91,59; 96,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,34; 96,37</t>
+          <t>92,14; 96,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 90,7</t>
+          <t>85,79; 91,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,9; 98,11</t>
+          <t>94,9; 98,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,82; 95,8</t>
+          <t>91,26; 95,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,05; 94,32</t>
+          <t>89,83; 94,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87,73; 91,66</t>
+          <t>87,0; 91,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94,39; 96,97</t>
+          <t>94,34; 96,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92,38; 95,59</t>
+          <t>92,31; 95,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91,84; 94,86</t>
+          <t>91,86; 94,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,22; 90,59</t>
+          <t>87,28; 90,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -1137,52 +1137,52 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,92; 93,75</t>
+          <t>91,94; 93,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92,48; 94,26</t>
+          <t>92,51; 94,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,76; 92,73</t>
+          <t>90,67; 92,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,56; 90,71</t>
+          <t>85,76; 88,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,47; 95,01</t>
+          <t>93,53; 95,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,29; 94,91</t>
+          <t>93,3; 94,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,28; 94,87</t>
+          <t>93,3; 94,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,05; 90,42</t>
+          <t>88,01; 89,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92,91; 94,19</t>
+          <t>93,01; 94,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93,13; 94,35</t>
+          <t>93,13; 94,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,38; 89,63</t>
+          <t>87,31; 88,93</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436813</t>
+          <t>489847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>677786</t>
+          <t>735793</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1114599</t>
+          <t>1225640</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>926170; 961808</t>
+          <t>926149; 960986</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>871719; 908233</t>
+          <t>871776; 907879</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>668669; 699989</t>
+          <t>668785; 699674</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>421946; 451868</t>
+          <t>472085; 506234</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1219670; 1252517</t>
+          <t>1220058; 1254146</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1249764; 1282088</t>
+          <t>1250104; 1283327</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>935613; 962337</t>
+          <t>938006; 964162</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>663327; 689501</t>
+          <t>722652; 748935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2157220; 2205330</t>
+          <t>2156295; 2207855</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2131995; 2182091</t>
+          <t>2134187; 2181149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1615802; 1655163</t>
+          <t>1614701; 1657162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1093294; 1133989</t>
+          <t>1201109; 1246461</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2034972</t>
+          <t>1948614</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1951748</t>
+          <t>1926212</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3986720</t>
+          <t>3874827</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1550986; 1594171</t>
+          <t>1549044; 1593642</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1823084; 1866282</t>
+          <t>1822907; 1866327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1860366; 1912140</t>
+          <t>1860485; 1914660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1986344; 2113263</t>
+          <t>1910159; 1983043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1465329; 1504130</t>
+          <t>1467014; 1504953</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1620621; 1663046</t>
+          <t>1619517; 1663224</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1838349; 1882205</t>
+          <t>1839630; 1880438</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1739082; 2036516</t>
+          <t>1897796; 1950270</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3030616; 3089811</t>
+          <t>3030102; 3088498</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3456645; 3519105</t>
+          <t>3455602; 3519857</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3713060; 3784144</t>
+          <t>3716872; 3784357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3777893; 4088714</t>
+          <t>3825760; 3920302</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569652</t>
+          <t>630917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>592655</t>
+          <t>656078</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1162307</t>
+          <t>1286995</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>509614; 532388</t>
+          <t>511324; 532332</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>439386; 463654</t>
+          <t>440723; 462854</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>504971; 527012</t>
+          <t>503885; 526749</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>552772; 586486</t>
+          <t>610452; 648567</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>452095; 467385</t>
+          <t>452104; 467335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>415715; 438505</t>
+          <t>417716; 438848</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>494505; 517938</t>
+          <t>493298; 519613</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>579418; 605406</t>
+          <t>639345; 668946</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>970208; 996658</t>
+          <t>969646; 996181</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>867349; 897510</t>
+          <t>866717; 896010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1006554; 1039671</t>
+          <t>1006863; 1040465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1140071; 1184137</t>
+          <t>1262526; 1309230</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3041438</t>
+          <t>3069380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3222190</t>
+          <t>3318082</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6263628</t>
+          <t>6387462</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3010865; 3070960</t>
+          <t>3011724; 3071974</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3161857; 3222662</t>
+          <t>3162803; 3222418</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3059384; 3125666</t>
+          <t>3056391; 3122667</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2987929; 3131048</t>
+          <t>3019514; 3109389</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3157344; 3209454</t>
+          <t>3159450; 3214503</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3310105; 3367822</t>
+          <t>3310519; 3366785</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3292093; 3348130</t>
+          <t>3292540; 3349211</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3034390; 3303809</t>
+          <t>3281441; 3349983</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6182195; 6267216</t>
+          <t>6188622; 6266671</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6488311; 6573248</t>
+          <t>6488830; 6574627</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6370552; 6457052</t>
+          <t>6370577; 6456893</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6067099; 6369040</t>
+          <t>6328816; 6446878</t>
         </is>
       </c>
     </row>
